--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -3684,7 +3684,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -3684,7 +3684,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -3684,7 +3684,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -3684,7 +3684,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -3684,7 +3684,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -3684,7 +3684,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -3684,7 +3684,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -3684,7 +3684,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -3684,7 +3684,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -3684,7 +3684,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -3684,7 +3684,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -3684,7 +3684,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -3684,7 +3684,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -3684,7 +3684,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -3684,7 +3684,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -3684,7 +3684,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -3684,7 +3684,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260129_201938.xlsx
@@ -3684,7 +3684,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
